--- a/Proiect/Proiect/Cleaned Data/gdp_cleaned.xlsx
+++ b/Proiect/Proiect/Cleaned Data/gdp_cleaned.xlsx
@@ -14,21 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Tara</t>
   </si>
   <si>
     <t>2023</t>
@@ -55,9 +43,15 @@
     <t>Denmark</t>
   </si>
   <si>
+    <t>Estonia</t>
+  </si>
+  <si>
     <t>Finland</t>
   </si>
   <si>
+    <t>France</t>
+  </si>
+  <si>
     <t>Germany</t>
   </si>
   <si>
@@ -73,6 +67,9 @@
     <t>Ireland</t>
   </si>
   <si>
+    <t>Italy</t>
+  </si>
+  <si>
     <t>Latvia</t>
   </si>
   <si>
@@ -85,7 +82,13 @@
     <t>Malta</t>
   </si>
   <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
     <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Norway</t>
   </si>
   <si>
     <t>Poland</t>
@@ -467,546 +470,262 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2">
+        <v>45670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3">
+        <v>44230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B4">
+        <v>10950</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="B5">
+        <v>16490</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
-        <v>45730</v>
-      </c>
-      <c r="C2">
-        <v>42650</v>
-      </c>
-      <c r="D2">
-        <v>44580</v>
-      </c>
-      <c r="E2">
-        <v>46430</v>
-      </c>
-      <c r="F2">
-        <v>45670</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B6">
+        <v>29200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>42400</v>
-      </c>
-      <c r="C3">
-        <v>40190</v>
-      </c>
-      <c r="D3">
-        <v>42530</v>
-      </c>
-      <c r="E3">
-        <v>43860</v>
-      </c>
-      <c r="F3">
-        <v>44230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B7">
+        <v>21680</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>9650</v>
-      </c>
-      <c r="C4">
-        <v>9440</v>
-      </c>
-      <c r="D4">
-        <v>10250</v>
-      </c>
-      <c r="E4">
-        <v>10740</v>
-      </c>
-      <c r="F4">
-        <v>10950</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B8">
+        <v>56470</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>14020</v>
-      </c>
-      <c r="C5">
-        <v>12980</v>
-      </c>
-      <c r="D5">
-        <v>14750</v>
-      </c>
-      <c r="E5">
-        <v>15900</v>
-      </c>
-      <c r="F5">
-        <v>16490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="B9">
+        <v>21210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>25790</v>
-      </c>
-      <c r="C6">
-        <v>24630</v>
-      </c>
-      <c r="D6">
-        <v>27030</v>
-      </c>
-      <c r="E6">
-        <v>28730</v>
-      </c>
-      <c r="F6">
-        <v>29200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="B10">
+        <v>43280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>22050</v>
-      </c>
-      <c r="C7">
-        <v>20980</v>
-      </c>
-      <c r="D7">
-        <v>21830</v>
-      </c>
-      <c r="E7">
-        <v>21910</v>
-      </c>
-      <c r="F7">
-        <v>21680</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="B11">
+        <v>37760</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>54630</v>
-      </c>
-      <c r="C8">
-        <v>53540</v>
-      </c>
-      <c r="D8">
-        <v>56780</v>
-      </c>
-      <c r="E8">
-        <v>56530</v>
-      </c>
-      <c r="F8">
-        <v>56470</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="B12">
+        <v>43450</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
-        <v>43910</v>
-      </c>
-      <c r="C9">
-        <v>42740</v>
-      </c>
-      <c r="D9">
-        <v>43800</v>
-      </c>
-      <c r="E9">
-        <v>44010</v>
-      </c>
-      <c r="F9">
-        <v>43280</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="B13">
+        <v>18600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
-        <v>43790</v>
-      </c>
-      <c r="C10">
-        <v>42020</v>
-      </c>
-      <c r="D10">
-        <v>43730</v>
-      </c>
-      <c r="E10">
-        <v>44230</v>
-      </c>
-      <c r="F10">
-        <v>43450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="B14">
+        <v>16050</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
-        <v>17210</v>
-      </c>
-      <c r="C11">
-        <v>15660</v>
-      </c>
-      <c r="D11">
-        <v>17110</v>
-      </c>
-      <c r="E11">
-        <v>18160</v>
-      </c>
-      <c r="F11">
-        <v>18600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="B15">
+        <v>61180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
-        <v>14980</v>
-      </c>
-      <c r="C12">
-        <v>14370</v>
-      </c>
-      <c r="D12">
-        <v>15470</v>
-      </c>
-      <c r="E12">
-        <v>16160</v>
-      </c>
-      <c r="F12">
-        <v>16050</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="B16">
+        <v>87810</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
-        <v>58770</v>
-      </c>
-      <c r="C13">
-        <v>54190</v>
-      </c>
-      <c r="D13">
-        <v>56150</v>
-      </c>
-      <c r="E13">
-        <v>59700</v>
-      </c>
-      <c r="F13">
-        <v>61180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="B17">
+        <v>32640</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
-        <v>71720</v>
-      </c>
-      <c r="C14">
-        <v>75820</v>
-      </c>
-      <c r="D14">
-        <v>87160</v>
-      </c>
-      <c r="E14">
-        <v>91760</v>
-      </c>
-      <c r="F14">
-        <v>87810</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="B18">
+        <v>16770</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
-        <v>15820</v>
-      </c>
-      <c r="C15">
-        <v>15370</v>
-      </c>
-      <c r="D15">
-        <v>16580</v>
-      </c>
-      <c r="E15">
-        <v>16890</v>
-      </c>
-      <c r="F15">
-        <v>16770</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="B19">
+        <v>19220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B16">
-        <v>17870</v>
-      </c>
-      <c r="C16">
-        <v>17890</v>
-      </c>
-      <c r="D16">
-        <v>19040</v>
-      </c>
-      <c r="E16">
-        <v>19350</v>
-      </c>
-      <c r="F16">
-        <v>19220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="B20">
+        <v>102250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B17">
-        <v>104310</v>
-      </c>
-      <c r="C17">
-        <v>102190</v>
-      </c>
-      <c r="D17">
-        <v>107570</v>
-      </c>
-      <c r="E17">
-        <v>104100</v>
-      </c>
-      <c r="F17">
-        <v>102250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="B21">
+        <v>33380</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B18">
-        <v>29480</v>
-      </c>
-      <c r="C18">
-        <v>27870</v>
-      </c>
-      <c r="D18">
-        <v>31420</v>
-      </c>
-      <c r="E18">
-        <v>31400</v>
-      </c>
-      <c r="F18">
-        <v>33380</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="B22">
+        <v>8620</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
-        <v>48970</v>
-      </c>
-      <c r="C19">
-        <v>46810</v>
-      </c>
-      <c r="D19">
-        <v>49490</v>
-      </c>
-      <c r="E19">
-        <v>51480</v>
-      </c>
-      <c r="F19">
+      <c r="B23">
         <v>50660</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B20">
-        <v>14310</v>
-      </c>
-      <c r="C20">
-        <v>14310</v>
-      </c>
-      <c r="D20">
-        <v>15380</v>
-      </c>
-      <c r="E20">
-        <v>15840</v>
-      </c>
-      <c r="F20">
+      <c r="B24">
+        <v>62790</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
         <v>15950</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21">
-        <v>21150</v>
-      </c>
-      <c r="C21">
-        <v>19360</v>
-      </c>
-      <c r="D21">
-        <v>20390</v>
-      </c>
-      <c r="E21">
-        <v>21690</v>
-      </c>
-      <c r="F21">
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
         <v>22130</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22">
-        <v>11760</v>
-      </c>
-      <c r="C22">
-        <v>11390</v>
-      </c>
-      <c r="D22">
-        <v>12130</v>
-      </c>
-      <c r="E22">
-        <v>12690</v>
-      </c>
-      <c r="F22">
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
         <v>12970</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23">
-        <v>17760</v>
-      </c>
-      <c r="C23">
-        <v>17270</v>
-      </c>
-      <c r="D23">
-        <v>18320</v>
-      </c>
-      <c r="E23">
-        <v>18360</v>
-      </c>
-      <c r="F23">
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
         <v>18750</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24">
-        <v>23330</v>
-      </c>
-      <c r="C24">
-        <v>22230</v>
-      </c>
-      <c r="D24">
-        <v>24040</v>
-      </c>
-      <c r="E24">
-        <v>24660</v>
-      </c>
-      <c r="F24">
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
         <v>25120</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25">
-        <v>26930</v>
-      </c>
-      <c r="C25">
-        <v>23850</v>
-      </c>
-      <c r="D25">
-        <v>25440</v>
-      </c>
-      <c r="E25">
-        <v>26820</v>
-      </c>
-      <c r="F25">
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
         <v>27150</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26">
-        <v>47410</v>
-      </c>
-      <c r="C26">
-        <v>46180</v>
-      </c>
-      <c r="D26">
-        <v>48300</v>
-      </c>
-      <c r="E26">
-        <v>48390</v>
-      </c>
-      <c r="F26">
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
         <v>47960</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27">
-        <v>79070</v>
-      </c>
-      <c r="C27">
-        <v>76710</v>
-      </c>
-      <c r="D27">
-        <v>80850</v>
-      </c>
-      <c r="E27">
-        <v>83000</v>
-      </c>
-      <c r="F27">
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
         <v>82440</v>
       </c>
     </row>

--- a/Proiect/Proiect/Cleaned Data/gdp_cleaned.xlsx
+++ b/Proiect/Proiect/Cleaned Data/gdp_cleaned.xlsx
@@ -14,20 +14,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Tara</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
+    <t>Albania</t>
+  </si>
+  <si>
     <t>Austria</t>
   </si>
   <si>
     <t>Belgium</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
     <t>Bulgaria</t>
   </si>
   <si>
@@ -70,9 +88,15 @@
     <t>Italy</t>
   </si>
   <si>
+    <t>Kosovo*</t>
+  </si>
+  <si>
     <t>Latvia</t>
   </si>
   <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -82,12 +106,18 @@
     <t>Malta</t>
   </si>
   <si>
+    <t>Moldova</t>
+  </si>
+  <si>
     <t>Montenegro</t>
   </si>
   <si>
     <t>Netherlands</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>Norway</t>
   </si>
   <si>
@@ -100,6 +130,9 @@
     <t>Romania</t>
   </si>
   <si>
+    <t>Serbia</t>
+  </si>
+  <si>
     <t>Slovakia</t>
   </si>
   <si>
@@ -113,6 +146,12 @@
   </si>
   <si>
     <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -470,263 +509,827 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2">
+        <v>4850</v>
+      </c>
+      <c r="C2">
+        <v>4710</v>
+      </c>
+      <c r="D2">
+        <v>5190</v>
+      </c>
+      <c r="E2">
+        <v>5500</v>
+      </c>
+      <c r="F2">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>45730</v>
+      </c>
+      <c r="C3">
+        <v>42650</v>
+      </c>
+      <c r="D3">
+        <v>44580</v>
+      </c>
+      <c r="E3">
+        <v>46430</v>
+      </c>
+      <c r="F3">
         <v>45670</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>42400</v>
+      </c>
+      <c r="C4">
+        <v>40190</v>
+      </c>
+      <c r="D4">
+        <v>42530</v>
+      </c>
+      <c r="E4">
+        <v>43860</v>
+      </c>
+      <c r="F4">
         <v>44230</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>31616</v>
+      </c>
+      <c r="C5">
+        <v>30446</v>
+      </c>
+      <c r="D5">
+        <v>32479.42857142857</v>
+      </c>
+      <c r="E5">
+        <v>33282</v>
+      </c>
+      <c r="F5">
+        <v>33208.57142857143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>9650</v>
+      </c>
+      <c r="C6">
+        <v>9440</v>
+      </c>
+      <c r="D6">
+        <v>10250</v>
+      </c>
+      <c r="E6">
+        <v>10740</v>
+      </c>
+      <c r="F6">
         <v>10950</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>14020</v>
+      </c>
+      <c r="C7">
+        <v>12980</v>
+      </c>
+      <c r="D7">
+        <v>14750</v>
+      </c>
+      <c r="E7">
+        <v>15900</v>
+      </c>
+      <c r="F7">
         <v>16490</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>25790</v>
+      </c>
+      <c r="C8">
+        <v>24630</v>
+      </c>
+      <c r="D8">
+        <v>27030</v>
+      </c>
+      <c r="E8">
+        <v>28730</v>
+      </c>
+      <c r="F8">
         <v>29200</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>22050</v>
+      </c>
+      <c r="C9">
+        <v>20980</v>
+      </c>
+      <c r="D9">
+        <v>21830</v>
+      </c>
+      <c r="E9">
+        <v>21910</v>
+      </c>
+      <c r="F9">
         <v>21680</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>54630</v>
+      </c>
+      <c r="C10">
+        <v>53540</v>
+      </c>
+      <c r="D10">
+        <v>56780</v>
+      </c>
+      <c r="E10">
+        <v>56530</v>
+      </c>
+      <c r="F10">
         <v>56470</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>21650</v>
+      </c>
+      <c r="C11">
+        <v>20960</v>
+      </c>
+      <c r="D11">
+        <v>22670</v>
+      </c>
+      <c r="E11">
+        <v>22370</v>
+      </c>
+      <c r="F11">
         <v>21210</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>43910</v>
+      </c>
+      <c r="C12">
+        <v>42740</v>
+      </c>
+      <c r="D12">
+        <v>43800</v>
+      </c>
+      <c r="E12">
+        <v>44010</v>
+      </c>
+      <c r="F12">
         <v>43280</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>37160</v>
+      </c>
+      <c r="C13">
+        <v>34280</v>
+      </c>
+      <c r="D13">
+        <v>36470</v>
+      </c>
+      <c r="E13">
+        <v>37320</v>
+      </c>
+      <c r="F13">
         <v>37760</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>43790</v>
+      </c>
+      <c r="C14">
+        <v>42020</v>
+      </c>
+      <c r="D14">
+        <v>43730</v>
+      </c>
+      <c r="E14">
+        <v>44230</v>
+      </c>
+      <c r="F14">
         <v>43450</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>17210</v>
+      </c>
+      <c r="C15">
+        <v>15660</v>
+      </c>
+      <c r="D15">
+        <v>17110</v>
+      </c>
+      <c r="E15">
+        <v>18160</v>
+      </c>
+      <c r="F15">
         <v>18600</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>14980</v>
+      </c>
+      <c r="C16">
+        <v>14370</v>
+      </c>
+      <c r="D16">
+        <v>15470</v>
+      </c>
+      <c r="E16">
+        <v>16160</v>
+      </c>
+      <c r="F16">
         <v>16050</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>58770</v>
+      </c>
+      <c r="C17">
+        <v>54190</v>
+      </c>
+      <c r="D17">
+        <v>56150</v>
+      </c>
+      <c r="E17">
+        <v>59700</v>
+      </c>
+      <c r="F17">
         <v>61180</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>71720</v>
+      </c>
+      <c r="C18">
+        <v>75820</v>
+      </c>
+      <c r="D18">
+        <v>87160</v>
+      </c>
+      <c r="E18">
+        <v>91760</v>
+      </c>
+      <c r="F18">
         <v>87810</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>30680</v>
+      </c>
+      <c r="C19">
+        <v>28100</v>
+      </c>
+      <c r="D19">
+        <v>30760</v>
+      </c>
+      <c r="E19">
+        <v>32310</v>
+      </c>
+      <c r="F19">
         <v>32640</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>31616</v>
+      </c>
+      <c r="C20">
+        <v>30446</v>
+      </c>
+      <c r="D20">
+        <v>32479.42857142857</v>
+      </c>
+      <c r="E20">
+        <v>33282</v>
+      </c>
+      <c r="F20">
+        <v>33208.57142857143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>15820</v>
+      </c>
+      <c r="C21">
+        <v>15370</v>
+      </c>
+      <c r="D21">
+        <v>16580</v>
+      </c>
+      <c r="E21">
+        <v>16890</v>
+      </c>
+      <c r="F21">
         <v>16770</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>31616</v>
+      </c>
+      <c r="C22">
+        <v>30446</v>
+      </c>
+      <c r="D22">
+        <v>32479.42857142857</v>
+      </c>
+      <c r="E22">
+        <v>33282</v>
+      </c>
+      <c r="F22">
+        <v>33208.57142857143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
+        <v>17870</v>
+      </c>
+      <c r="C23">
+        <v>17890</v>
+      </c>
+      <c r="D23">
+        <v>19040</v>
+      </c>
+      <c r="E23">
+        <v>19350</v>
+      </c>
+      <c r="F23">
         <v>19220</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
+        <v>104310</v>
+      </c>
+      <c r="C24">
+        <v>102190</v>
+      </c>
+      <c r="D24">
+        <v>107570</v>
+      </c>
+      <c r="E24">
+        <v>104100</v>
+      </c>
+      <c r="F24">
         <v>102250</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25">
+        <v>29480</v>
+      </c>
+      <c r="C25">
+        <v>27870</v>
+      </c>
+      <c r="D25">
+        <v>31420</v>
+      </c>
+      <c r="E25">
+        <v>31400</v>
+      </c>
+      <c r="F25">
         <v>33380</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26">
+        <v>31616</v>
+      </c>
+      <c r="C26">
+        <v>30446</v>
+      </c>
+      <c r="D26">
+        <v>32479.42857142857</v>
+      </c>
+      <c r="E26">
+        <v>33282</v>
+      </c>
+      <c r="F26">
+        <v>33208.57142857143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27">
+        <v>7780</v>
+      </c>
+      <c r="C27">
+        <v>6610</v>
+      </c>
+      <c r="D27">
+        <v>7500</v>
+      </c>
+      <c r="E27">
+        <v>8100</v>
+      </c>
+      <c r="F27">
         <v>8620</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>48970</v>
+      </c>
+      <c r="C28">
+        <v>46810</v>
+      </c>
+      <c r="D28">
+        <v>49490</v>
+      </c>
+      <c r="E28">
+        <v>51480</v>
+      </c>
+      <c r="F28">
         <v>50660</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>6070</v>
+      </c>
+      <c r="C29">
+        <v>5840</v>
+      </c>
+      <c r="D29">
+        <v>6170</v>
+      </c>
+      <c r="E29">
+        <v>6360</v>
+      </c>
+      <c r="F29">
+        <v>6540</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30">
+        <v>61150</v>
+      </c>
+      <c r="C30">
+        <v>60020</v>
+      </c>
+      <c r="D30">
+        <v>62030</v>
+      </c>
+      <c r="E30">
+        <v>63470</v>
+      </c>
+      <c r="F30">
         <v>62790</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31">
+        <v>14310</v>
+      </c>
+      <c r="C31">
+        <v>14310</v>
+      </c>
+      <c r="D31">
+        <v>15380</v>
+      </c>
+      <c r="E31">
+        <v>15840</v>
+      </c>
+      <c r="F31">
         <v>15950</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>21150</v>
+      </c>
+      <c r="C32">
+        <v>19360</v>
+      </c>
+      <c r="D32">
+        <v>20390</v>
+      </c>
+      <c r="E32">
+        <v>21690</v>
+      </c>
+      <c r="F32">
         <v>22130</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>11760</v>
+      </c>
+      <c r="C33">
+        <v>11390</v>
+      </c>
+      <c r="D33">
+        <v>12130</v>
+      </c>
+      <c r="E33">
+        <v>12690</v>
+      </c>
+      <c r="F33">
         <v>12970</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>7130</v>
+      </c>
+      <c r="C34">
+        <v>7110</v>
+      </c>
+      <c r="D34">
+        <v>7740</v>
+      </c>
+      <c r="E34">
+        <v>8160</v>
+      </c>
+      <c r="F34">
+        <v>8510</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
+        <v>17760</v>
+      </c>
+      <c r="C35">
+        <v>17270</v>
+      </c>
+      <c r="D35">
+        <v>18320</v>
+      </c>
+      <c r="E35">
+        <v>18360</v>
+      </c>
+      <c r="F35">
         <v>18750</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36">
+        <v>23330</v>
+      </c>
+      <c r="C36">
+        <v>22230</v>
+      </c>
+      <c r="D36">
+        <v>24040</v>
+      </c>
+      <c r="E36">
+        <v>24660</v>
+      </c>
+      <c r="F36">
         <v>25120</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>26930</v>
+      </c>
+      <c r="C37">
+        <v>23850</v>
+      </c>
+      <c r="D37">
+        <v>25440</v>
+      </c>
+      <c r="E37">
+        <v>26820</v>
+      </c>
+      <c r="F37">
         <v>27150</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38">
+        <v>47410</v>
+      </c>
+      <c r="C38">
+        <v>46180</v>
+      </c>
+      <c r="D38">
+        <v>48300</v>
+      </c>
+      <c r="E38">
+        <v>48390</v>
+      </c>
+      <c r="F38">
         <v>47960</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39">
+        <v>79070</v>
+      </c>
+      <c r="C39">
+        <v>76710</v>
+      </c>
+      <c r="D39">
+        <v>80850</v>
+      </c>
+      <c r="E39">
+        <v>83000</v>
+      </c>
+      <c r="F39">
         <v>82440</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40">
+        <v>7270</v>
+      </c>
+      <c r="C40">
+        <v>7340</v>
+      </c>
+      <c r="D40">
+        <v>8130</v>
+      </c>
+      <c r="E40">
+        <v>8490</v>
+      </c>
+      <c r="F40">
+        <v>8920</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41">
+        <v>31616</v>
+      </c>
+      <c r="C41">
+        <v>30446</v>
+      </c>
+      <c r="D41">
+        <v>32479.42857142857</v>
+      </c>
+      <c r="E41">
+        <v>33282</v>
+      </c>
+      <c r="F41">
+        <v>33208.57142857143</v>
       </c>
     </row>
   </sheetData>
